--- a/02_Excel/Ujjsha_Retail_Project1.xlsx
+++ b/02_Excel/Ujjsha_Retail_Project1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ujjwalpoudel/Desktop/DataAnalyticsJourney/02_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EF6A5F-EB8A-964A-BF41-E238DF867401}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B24C03-9795-C141-A468-C82788A5C0F3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{F345E6D1-68A7-DD4A-93A9-6734491FC4EE}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="7" xr2:uid="{F345E6D1-68A7-DD4A-93A9-6734491FC4EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
-    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="17" r:id="rId9"/>
+    <pivotCache cacheId="12" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="79">
   <si>
     <t>sale_id</t>
   </si>
@@ -244,11 +244,56 @@
   <si>
     <t>revenue</t>
   </si>
+  <si>
+    <t>Sum of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">August - July </t>
+  </si>
+  <si>
+    <t>Revenue % Change</t>
+  </si>
+  <si>
+    <t>Revenue Per Transaction</t>
+  </si>
+  <si>
+    <t>Revenue Analysis between July and August</t>
+  </si>
+  <si>
+    <t>Revenue Change</t>
+  </si>
+  <si>
+    <t>Category-level Revenue Analysis</t>
+  </si>
+  <si>
+    <t>Product-level Revenue Analysis</t>
+  </si>
+  <si>
+    <t>Average of unit_price</t>
+  </si>
+  <si>
+    <t>Rev/ Tran % increase</t>
+  </si>
+  <si>
+    <t>Average revenue per unit by month</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>Total Revenue/Total Units Sold</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.000000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -266,7 +311,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,8 +330,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -303,11 +354,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -325,6 +385,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -364,274 +435,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="46268.925071759259" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="55" xr:uid="{40EC24C7-A6FC-7E43-ADB1-2BCD69897D8F}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="InventoryTable"/>
-  </cacheSource>
-  <cacheFields count="5">
-    <cacheField name="inventory_id" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="55"/>
-    </cacheField>
-    <cacheField name="product_id" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
-    </cacheField>
-    <cacheField name="product_name" numFmtId="0">
-      <sharedItems count="25">
-        <s v="Wireless Mouse"/>
-        <s v="USB-C Cable"/>
-        <s v="Laptop Stand"/>
-        <s v="Webcam Cover"/>
-        <s v="Mouse Pad"/>
-        <s v="Business Laptop"/>
-        <s v="Gaming Laptop"/>
-        <s v="Desktop Computer"/>
-        <s v="Mini PC"/>
-        <s v="Workstation"/>
-        <s v="Bluetooth Speaker"/>
-        <s v="Wireless Headphones"/>
-        <s v="Soundbar"/>
-        <s v="USB Microphone"/>
-        <s v="Wireless Earbuds"/>
-        <s v="Office Chair"/>
-        <s v="Desk Lamp"/>
-        <s v="Standing Desk"/>
-        <s v="Monitor Arm"/>
-        <s v="Keyboard Tray"/>
-        <s v="Wi-Fi Router"/>
-        <s v="Network Switch"/>
-        <s v="Wi-Fi Extender"/>
-        <s v="Ethernet Adapter"/>
-        <s v="Mesh Wi-Fi System"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="warehouse" numFmtId="0">
-      <sharedItems count="3">
-        <s v="New York"/>
-        <s v="Dallas"/>
-        <s v="Chicago"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="stock_quantity" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="261"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="46268.925071759259" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="200" xr:uid="{C9DA8EF7-74CB-9D4D-A6B2-716F7EA54D97}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="46270.885065972223" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="200" xr:uid="{C9DA8EF7-74CB-9D4D-A6B2-716F7EA54D97}">
   <cacheSource type="worksheet">
     <worksheetSource name="SalesTable"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="9">
     <cacheField name="sale_id" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="200" count="200">
-        <n v="1"/>
-        <n v="2"/>
-        <n v="3"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="6"/>
-        <n v="7"/>
-        <n v="8"/>
-        <n v="9"/>
-        <n v="10"/>
-        <n v="11"/>
-        <n v="12"/>
-        <n v="13"/>
-        <n v="14"/>
-        <n v="15"/>
-        <n v="16"/>
-        <n v="17"/>
-        <n v="18"/>
-        <n v="19"/>
-        <n v="20"/>
-        <n v="21"/>
-        <n v="22"/>
-        <n v="23"/>
-        <n v="24"/>
-        <n v="25"/>
-        <n v="26"/>
-        <n v="27"/>
-        <n v="28"/>
-        <n v="29"/>
-        <n v="30"/>
-        <n v="31"/>
-        <n v="32"/>
-        <n v="33"/>
-        <n v="34"/>
-        <n v="35"/>
-        <n v="36"/>
-        <n v="37"/>
-        <n v="38"/>
-        <n v="39"/>
-        <n v="40"/>
-        <n v="41"/>
-        <n v="42"/>
-        <n v="43"/>
-        <n v="44"/>
-        <n v="45"/>
-        <n v="46"/>
-        <n v="47"/>
-        <n v="48"/>
-        <n v="49"/>
-        <n v="50"/>
-        <n v="51"/>
-        <n v="52"/>
-        <n v="53"/>
-        <n v="54"/>
-        <n v="55"/>
-        <n v="56"/>
-        <n v="57"/>
-        <n v="58"/>
-        <n v="59"/>
-        <n v="60"/>
-        <n v="61"/>
-        <n v="62"/>
-        <n v="63"/>
-        <n v="64"/>
-        <n v="65"/>
-        <n v="66"/>
-        <n v="67"/>
-        <n v="68"/>
-        <n v="69"/>
-        <n v="70"/>
-        <n v="71"/>
-        <n v="72"/>
-        <n v="73"/>
-        <n v="74"/>
-        <n v="75"/>
-        <n v="76"/>
-        <n v="77"/>
-        <n v="78"/>
-        <n v="79"/>
-        <n v="80"/>
-        <n v="81"/>
-        <n v="82"/>
-        <n v="83"/>
-        <n v="84"/>
-        <n v="85"/>
-        <n v="86"/>
-        <n v="87"/>
-        <n v="88"/>
-        <n v="89"/>
-        <n v="90"/>
-        <n v="91"/>
-        <n v="92"/>
-        <n v="93"/>
-        <n v="94"/>
-        <n v="95"/>
-        <n v="96"/>
-        <n v="97"/>
-        <n v="98"/>
-        <n v="99"/>
-        <n v="100"/>
-        <n v="101"/>
-        <n v="102"/>
-        <n v="103"/>
-        <n v="104"/>
-        <n v="105"/>
-        <n v="106"/>
-        <n v="107"/>
-        <n v="108"/>
-        <n v="109"/>
-        <n v="110"/>
-        <n v="111"/>
-        <n v="112"/>
-        <n v="113"/>
-        <n v="114"/>
-        <n v="115"/>
-        <n v="116"/>
-        <n v="117"/>
-        <n v="118"/>
-        <n v="119"/>
-        <n v="120"/>
-        <n v="121"/>
-        <n v="122"/>
-        <n v="123"/>
-        <n v="124"/>
-        <n v="125"/>
-        <n v="126"/>
-        <n v="127"/>
-        <n v="128"/>
-        <n v="129"/>
-        <n v="130"/>
-        <n v="131"/>
-        <n v="132"/>
-        <n v="133"/>
-        <n v="134"/>
-        <n v="135"/>
-        <n v="136"/>
-        <n v="137"/>
-        <n v="138"/>
-        <n v="139"/>
-        <n v="140"/>
-        <n v="141"/>
-        <n v="142"/>
-        <n v="143"/>
-        <n v="144"/>
-        <n v="145"/>
-        <n v="146"/>
-        <n v="147"/>
-        <n v="148"/>
-        <n v="149"/>
-        <n v="150"/>
-        <n v="151"/>
-        <n v="152"/>
-        <n v="153"/>
-        <n v="154"/>
-        <n v="155"/>
-        <n v="156"/>
-        <n v="157"/>
-        <n v="158"/>
-        <n v="159"/>
-        <n v="160"/>
-        <n v="161"/>
-        <n v="162"/>
-        <n v="163"/>
-        <n v="164"/>
-        <n v="165"/>
-        <n v="166"/>
-        <n v="167"/>
-        <n v="168"/>
-        <n v="169"/>
-        <n v="170"/>
-        <n v="171"/>
-        <n v="172"/>
-        <n v="173"/>
-        <n v="174"/>
-        <n v="175"/>
-        <n v="176"/>
-        <n v="177"/>
-        <n v="178"/>
-        <n v="179"/>
-        <n v="180"/>
-        <n v="181"/>
-        <n v="182"/>
-        <n v="183"/>
-        <n v="184"/>
-        <n v="185"/>
-        <n v="186"/>
-        <n v="187"/>
-        <n v="188"/>
-        <n v="189"/>
-        <n v="190"/>
-        <n v="191"/>
-        <n v="192"/>
-        <n v="193"/>
-        <n v="194"/>
-        <n v="195"/>
-        <n v="196"/>
-        <n v="197"/>
-        <n v="198"/>
-        <n v="199"/>
-        <n v="200"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="200"/>
     </cacheField>
     <cacheField name="product_id" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
@@ -715,7 +525,7 @@
         <d v="2026-06-16T00:00:00"/>
         <d v="2026-08-17T00:00:00"/>
       </sharedItems>
-      <fieldGroup par="6" base="2">
+      <fieldGroup par="8" base="2">
         <rangePr groupBy="days" startDate="2026-05-21T00:00:00" endDate="2026-08-19T00:00:00"/>
         <groupItems count="368">
           <s v="&lt;5/21/26"/>
@@ -1090,18 +900,7 @@
       </fieldGroup>
     </cacheField>
     <cacheField name="quantity" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10" count="10">
-        <n v="8"/>
-        <n v="5"/>
-        <n v="9"/>
-        <n v="2"/>
-        <n v="3"/>
-        <n v="1"/>
-        <n v="4"/>
-        <n v="6"/>
-        <n v="7"/>
-        <n v="10"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
     </cacheField>
     <cacheField name="product_name" numFmtId="0">
       <sharedItems count="25">
@@ -1141,6 +940,156 @@
         <s v="Networking"/>
       </sharedItems>
     </cacheField>
+    <cacheField name="unit_price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="17.239999999999998" maxValue="1387.44" count="25">
+        <n v="62.84"/>
+        <n v="17.239999999999998"/>
+        <n v="38.270000000000003"/>
+        <n v="71.17"/>
+        <n v="31.46"/>
+        <n v="146.37"/>
+        <n v="1107.2"/>
+        <n v="1387.44"/>
+        <n v="844.86"/>
+        <n v="718.81"/>
+        <n v="233.04"/>
+        <n v="358.79"/>
+        <n v="487.7"/>
+        <n v="176.19"/>
+        <n v="250.32"/>
+        <n v="282.3"/>
+        <n v="25.28"/>
+        <n v="191.24"/>
+        <n v="250.25"/>
+        <n v="62.2"/>
+        <n v="147.08000000000001"/>
+        <n v="341.92"/>
+        <n v="519.54999999999995"/>
+        <n v="486.94"/>
+        <n v="472.01"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="revenue" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="17.239999999999998" maxValue="4162.32" count="117">
+        <n v="502.72"/>
+        <n v="86.199999999999989"/>
+        <n v="344.43"/>
+        <n v="569.36"/>
+        <n v="251.68"/>
+        <n v="292.74"/>
+        <n v="3321.6000000000004"/>
+        <n v="4162.32"/>
+        <n v="844.86"/>
+        <n v="2156.4299999999998"/>
+        <n v="233.04"/>
+        <n v="1435.16"/>
+        <n v="2926.2"/>
+        <n v="880.95"/>
+        <n v="750.96"/>
+        <n v="1129.2"/>
+        <n v="50.56"/>
+        <n v="956.2"/>
+        <n v="250.25"/>
+        <n v="124.4"/>
+        <n v="1029.5600000000002"/>
+        <n v="1025.76"/>
+        <n v="519.54999999999995"/>
+        <n v="3895.52"/>
+        <n v="1888.04"/>
+        <n v="975.4"/>
+        <n v="2921.64"/>
+        <n v="314.60000000000002"/>
+        <n v="2393.44"/>
+        <n v="2774.88"/>
+        <n v="2534.58"/>
+        <n v="25.28"/>
+        <n v="1076.3700000000001"/>
+        <n v="1165.2"/>
+        <n v="147.08000000000001"/>
+        <n v="157.30000000000001"/>
+        <n v="101.12"/>
+        <n v="735.40000000000009"/>
+        <n v="1437.62"/>
+        <n v="1251.5999999999999"/>
+        <n v="248.8"/>
+        <n v="1558.6499999999999"/>
+        <n v="2214.4"/>
+        <n v="3304.0699999999997"/>
+        <n v="3636.8499999999995"/>
+        <n v="146.37"/>
+        <n v="1001"/>
+        <n v="341.92"/>
+        <n v="1001.28"/>
+        <n v="38.270000000000003"/>
+        <n v="500.64"/>
+        <n v="528.56999999999994"/>
+        <n v="717.58"/>
+        <n v="439.88"/>
+        <n v="699.12"/>
+        <n v="628.40000000000009"/>
+        <n v="2832.06"/>
+        <n v="1689.72"/>
+        <n v="588.32000000000005"/>
+        <n v="125.84"/>
+        <n v="51.72"/>
+        <n v="1057.1399999999999"/>
+        <n v="486.94"/>
+        <n v="17.239999999999998"/>
+        <n v="294.16000000000003"/>
+        <n v="573.72"/>
+        <n v="126.4"/>
+        <n v="284.68"/>
+        <n v="103.44"/>
+        <n v="565.56000000000006"/>
+        <n v="1501.92"/>
+        <n v="704.76"/>
+        <n v="62.2"/>
+        <n v="94.38"/>
+        <n v="3408.58"/>
+        <n v="1709.6000000000001"/>
+        <n v="1947.76"/>
+        <n v="2438.5"/>
+        <n v="188.52"/>
+        <n v="487.7"/>
+        <n v="498.19"/>
+        <n v="1251.25"/>
+        <n v="314.20000000000005"/>
+        <n v="932.16"/>
+        <n v="76.540000000000006"/>
+        <n v="466.08"/>
+        <n v="176.19"/>
+        <n v="153.08000000000001"/>
+        <n v="1411.5"/>
+        <n v="4156.3999999999996"/>
+        <n v="282.3"/>
+        <n v="750.75"/>
+        <n v="1460.82"/>
+        <n v="718.81"/>
+        <n v="188.76"/>
+        <n v="191.24"/>
+        <n v="125.68"/>
+        <n v="382.48"/>
+        <n v="283.14"/>
+        <n v="358.79"/>
+        <n v="1107.2"/>
+        <n v="2434.6999999999998"/>
+        <n v="1387.44"/>
+        <n v="944.02"/>
+        <n v="220.22"/>
+        <n v="3776.08"/>
+        <n v="71.17"/>
+        <n v="439.11"/>
+        <n v="683.84"/>
+        <n v="1793.95"/>
+        <n v="75.84"/>
+        <n v="2152.7400000000002"/>
+        <n v="2597.75"/>
+        <n v="2360.0500000000002"/>
+        <n v="142.34"/>
+        <n v="1039.0999999999999"/>
+        <n v="3117.2999999999997"/>
+      </sharedItems>
+    </cacheField>
     <cacheField name="Months" numFmtId="0" databaseField="0">
       <fieldGroup base="2">
         <rangePr groupBy="months" startDate="2026-05-21T00:00:00" endDate="2026-08-19T00:00:00"/>
@@ -1171,7 +1120,2072 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="46270.885066435185" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="55" xr:uid="{40EC24C7-A6FC-7E43-ADB1-2BCD69897D8F}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="InventoryTable"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="inventory_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="55"/>
+    </cacheField>
+    <cacheField name="product_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
+    </cacheField>
+    <cacheField name="product_name" numFmtId="0">
+      <sharedItems count="25">
+        <s v="Wireless Mouse"/>
+        <s v="USB-C Cable"/>
+        <s v="Laptop Stand"/>
+        <s v="Webcam Cover"/>
+        <s v="Mouse Pad"/>
+        <s v="Business Laptop"/>
+        <s v="Gaming Laptop"/>
+        <s v="Desktop Computer"/>
+        <s v="Mini PC"/>
+        <s v="Workstation"/>
+        <s v="Bluetooth Speaker"/>
+        <s v="Wireless Headphones"/>
+        <s v="Soundbar"/>
+        <s v="USB Microphone"/>
+        <s v="Wireless Earbuds"/>
+        <s v="Office Chair"/>
+        <s v="Desk Lamp"/>
+        <s v="Standing Desk"/>
+        <s v="Monitor Arm"/>
+        <s v="Keyboard Tray"/>
+        <s v="Wi-Fi Router"/>
+        <s v="Network Switch"/>
+        <s v="Wi-Fi Extender"/>
+        <s v="Ethernet Adapter"/>
+        <s v="Mesh Wi-Fi System"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="warehouse" numFmtId="0">
+      <sharedItems count="3">
+        <s v="New York"/>
+        <s v="Dallas"/>
+        <s v="Chicago"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="stock_quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="261"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="200">
+  <r>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="2"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="4"/>
+    <x v="3"/>
+    <n v="8"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="5"/>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="6"/>
+    <x v="5"/>
+    <n v="2"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="7"/>
+    <x v="6"/>
+    <n v="3"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="8"/>
+    <x v="7"/>
+    <n v="3"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="1"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="10"/>
+    <x v="9"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="11"/>
+    <x v="10"/>
+    <n v="1"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="12"/>
+    <x v="11"/>
+    <n v="4"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="13"/>
+    <x v="12"/>
+    <n v="6"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="14"/>
+    <x v="13"/>
+    <n v="5"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="14"/>
+    <n v="3"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="16"/>
+    <x v="15"/>
+    <n v="4"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="17"/>
+    <x v="16"/>
+    <n v="2"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="18"/>
+    <x v="3"/>
+    <n v="5"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="19"/>
+    <x v="17"/>
+    <n v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="20"/>
+    <x v="18"/>
+    <n v="2"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="21"/>
+    <x v="10"/>
+    <n v="7"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="22"/>
+    <x v="19"/>
+    <n v="3"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="23"/>
+    <x v="7"/>
+    <n v="1"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="24"/>
+    <x v="14"/>
+    <n v="8"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="25"/>
+    <x v="20"/>
+    <n v="4"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="13"/>
+    <x v="10"/>
+    <n v="2"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="2"/>
+    <x v="21"/>
+    <n v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="24"/>
+    <x v="22"/>
+    <n v="6"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="5"/>
+    <x v="23"/>
+    <n v="10"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="22"/>
+    <x v="2"/>
+    <n v="7"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="8"/>
+    <x v="24"/>
+    <n v="2"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="9"/>
+    <x v="25"/>
+    <n v="3"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="17"/>
+    <x v="26"/>
+    <n v="1"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="12"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="11"/>
+    <x v="27"/>
+    <n v="5"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="21"/>
+    <x v="28"/>
+    <n v="1"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="5"/>
+    <x v="29"/>
+    <n v="5"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="17"/>
+    <x v="30"/>
+    <n v="4"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="21"/>
+    <x v="31"/>
+    <n v="5"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="37"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="10"/>
+    <x v="32"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="15"/>
+    <x v="27"/>
+    <n v="5"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="39"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="20"/>
+    <x v="10"/>
+    <n v="4"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="40"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="23"/>
+    <x v="33"/>
+    <n v="3"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="41"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="10"/>
+    <x v="5"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="9"/>
+    <x v="3"/>
+    <n v="3"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="7"/>
+    <x v="11"/>
+    <n v="2"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="42"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="25"/>
+    <x v="34"/>
+    <n v="7"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="6"/>
+    <x v="35"/>
+    <n v="2"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="23"/>
+    <x v="36"/>
+    <n v="7"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="44"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="6"/>
+    <x v="25"/>
+    <n v="1"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="45"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <n v="19"/>
+    <x v="37"/>
+    <n v="4"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="46"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <n v="22"/>
+    <x v="38"/>
+    <n v="1"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="47"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <n v="15"/>
+    <x v="12"/>
+    <n v="4"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="48"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <n v="3"/>
+    <x v="39"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="49"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <n v="15"/>
+    <x v="40"/>
+    <n v="2"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="50"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <n v="14"/>
+    <x v="41"/>
+    <n v="3"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="51"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <n v="12"/>
+    <x v="42"/>
+    <n v="2"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="52"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <n v="10"/>
+    <x v="22"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <n v="1"/>
+    <x v="38"/>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="53"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <n v="11"/>
+    <x v="43"/>
+    <n v="3"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="54"/>
+  </r>
+  <r>
+    <n v="61"/>
+    <n v="1"/>
+    <x v="44"/>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="55"/>
+  </r>
+  <r>
+    <n v="62"/>
+    <n v="25"/>
+    <x v="11"/>
+    <n v="6"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="56"/>
+  </r>
+  <r>
+    <n v="63"/>
+    <n v="9"/>
+    <x v="45"/>
+    <n v="2"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="57"/>
+  </r>
+  <r>
+    <n v="64"/>
+    <n v="19"/>
+    <x v="24"/>
+    <n v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="65"/>
+    <n v="21"/>
+    <x v="29"/>
+    <n v="4"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="58"/>
+  </r>
+  <r>
+    <n v="66"/>
+    <n v="5"/>
+    <x v="46"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="59"/>
+  </r>
+  <r>
+    <n v="67"/>
+    <n v="2"/>
+    <x v="5"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="60"/>
+  </r>
+  <r>
+    <n v="68"/>
+    <n v="14"/>
+    <x v="19"/>
+    <n v="6"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="61"/>
+  </r>
+  <r>
+    <n v="69"/>
+    <n v="24"/>
+    <x v="43"/>
+    <n v="1"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="62"/>
+  </r>
+  <r>
+    <n v="70"/>
+    <n v="20"/>
+    <x v="19"/>
+    <n v="2"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="71"/>
+    <n v="8"/>
+    <x v="47"/>
+    <n v="2"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <n v="72"/>
+    <n v="2"/>
+    <x v="39"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="63"/>
+  </r>
+  <r>
+    <n v="73"/>
+    <n v="25"/>
+    <x v="48"/>
+    <n v="7"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <n v="74"/>
+    <n v="25"/>
+    <x v="2"/>
+    <n v="7"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <n v="75"/>
+    <n v="21"/>
+    <x v="49"/>
+    <n v="2"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="64"/>
+  </r>
+  <r>
+    <n v="76"/>
+    <n v="19"/>
+    <x v="30"/>
+    <n v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="77"/>
+    <n v="17"/>
+    <x v="50"/>
+    <n v="1"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <n v="78"/>
+    <n v="11"/>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="79"/>
+    <n v="18"/>
+    <x v="51"/>
+    <n v="3"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="65"/>
+  </r>
+  <r>
+    <n v="80"/>
+    <n v="17"/>
+    <x v="52"/>
+    <n v="5"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="66"/>
+  </r>
+  <r>
+    <n v="81"/>
+    <n v="4"/>
+    <x v="53"/>
+    <n v="4"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="67"/>
+  </r>
+  <r>
+    <n v="82"/>
+    <n v="2"/>
+    <x v="20"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="68"/>
+  </r>
+  <r>
+    <n v="83"/>
+    <n v="1"/>
+    <x v="29"/>
+    <n v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="69"/>
+  </r>
+  <r>
+    <n v="84"/>
+    <n v="15"/>
+    <x v="54"/>
+    <n v="6"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="70"/>
+  </r>
+  <r>
+    <n v="85"/>
+    <n v="14"/>
+    <x v="32"/>
+    <n v="4"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="71"/>
+  </r>
+  <r>
+    <n v="86"/>
+    <n v="20"/>
+    <x v="42"/>
+    <n v="1"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="72"/>
+  </r>
+  <r>
+    <n v="87"/>
+    <n v="5"/>
+    <x v="13"/>
+    <n v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="73"/>
+  </r>
+  <r>
+    <n v="88"/>
+    <n v="24"/>
+    <x v="55"/>
+    <n v="7"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="74"/>
+  </r>
+  <r>
+    <n v="89"/>
+    <n v="22"/>
+    <x v="56"/>
+    <n v="5"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="75"/>
+  </r>
+  <r>
+    <n v="90"/>
+    <n v="24"/>
+    <x v="46"/>
+    <n v="4"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="76"/>
+  </r>
+  <r>
+    <n v="91"/>
+    <n v="25"/>
+    <x v="6"/>
+    <n v="6"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="56"/>
+  </r>
+  <r>
+    <n v="92"/>
+    <n v="22"/>
+    <x v="57"/>
+    <n v="5"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="75"/>
+  </r>
+  <r>
+    <n v="93"/>
+    <n v="12"/>
+    <x v="58"/>
+    <n v="4"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="94"/>
+    <n v="17"/>
+    <x v="3"/>
+    <n v="2"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="95"/>
+    <n v="13"/>
+    <x v="37"/>
+    <n v="5"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="77"/>
+  </r>
+  <r>
+    <n v="96"/>
+    <n v="25"/>
+    <x v="8"/>
+    <n v="6"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="56"/>
+  </r>
+  <r>
+    <n v="97"/>
+    <n v="9"/>
+    <x v="24"/>
+    <n v="2"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="57"/>
+  </r>
+  <r>
+    <n v="98"/>
+    <n v="1"/>
+    <x v="59"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="78"/>
+  </r>
+  <r>
+    <n v="99"/>
+    <n v="13"/>
+    <x v="34"/>
+    <n v="1"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="79"/>
+  </r>
+  <r>
+    <n v="100"/>
+    <n v="7"/>
+    <x v="57"/>
+    <n v="2"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="42"/>
+  </r>
+  <r>
+    <n v="101"/>
+    <n v="9"/>
+    <x v="16"/>
+    <n v="2"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="57"/>
+  </r>
+  <r>
+    <n v="102"/>
+    <n v="11"/>
+    <x v="59"/>
+    <n v="3"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="54"/>
+  </r>
+  <r>
+    <n v="103"/>
+    <n v="4"/>
+    <x v="9"/>
+    <n v="7"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="80"/>
+  </r>
+  <r>
+    <n v="104"/>
+    <n v="21"/>
+    <x v="29"/>
+    <n v="7"/>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="105"/>
+    <n v="19"/>
+    <x v="44"/>
+    <n v="5"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="81"/>
+  </r>
+  <r>
+    <n v="106"/>
+    <n v="17"/>
+    <x v="60"/>
+    <n v="4"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <n v="107"/>
+    <n v="8"/>
+    <x v="61"/>
+    <n v="3"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="108"/>
+    <n v="15"/>
+    <x v="2"/>
+    <n v="5"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="39"/>
+  </r>
+  <r>
+    <n v="109"/>
+    <n v="6"/>
+    <x v="3"/>
+    <n v="2"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="110"/>
+    <n v="1"/>
+    <x v="62"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="82"/>
+  </r>
+  <r>
+    <n v="111"/>
+    <n v="11"/>
+    <x v="16"/>
+    <n v="4"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="83"/>
+  </r>
+  <r>
+    <n v="112"/>
+    <n v="24"/>
+    <x v="49"/>
+    <n v="6"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <n v="113"/>
+    <n v="3"/>
+    <x v="40"/>
+    <n v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="84"/>
+  </r>
+  <r>
+    <n v="114"/>
+    <n v="19"/>
+    <x v="22"/>
+    <n v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="115"/>
+    <n v="24"/>
+    <x v="63"/>
+    <n v="1"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="62"/>
+  </r>
+  <r>
+    <n v="116"/>
+    <n v="11"/>
+    <x v="64"/>
+    <n v="2"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="85"/>
+  </r>
+  <r>
+    <n v="117"/>
+    <n v="9"/>
+    <x v="65"/>
+    <n v="3"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <n v="118"/>
+    <n v="14"/>
+    <x v="66"/>
+    <n v="1"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="86"/>
+  </r>
+  <r>
+    <n v="119"/>
+    <n v="10"/>
+    <x v="33"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="120"/>
+    <n v="2"/>
+    <x v="46"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="63"/>
+  </r>
+  <r>
+    <n v="121"/>
+    <n v="3"/>
+    <x v="42"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="87"/>
+  </r>
+  <r>
+    <n v="122"/>
+    <n v="23"/>
+    <x v="19"/>
+    <n v="7"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="44"/>
+  </r>
+  <r>
+    <n v="123"/>
+    <n v="16"/>
+    <x v="28"/>
+    <n v="5"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="88"/>
+  </r>
+  <r>
+    <n v="124"/>
+    <n v="15"/>
+    <x v="56"/>
+    <n v="3"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="125"/>
+    <n v="23"/>
+    <x v="67"/>
+    <n v="8"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="89"/>
+  </r>
+  <r>
+    <n v="126"/>
+    <n v="16"/>
+    <x v="28"/>
+    <n v="5"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="88"/>
+  </r>
+  <r>
+    <n v="127"/>
+    <n v="16"/>
+    <x v="24"/>
+    <n v="1"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="90"/>
+  </r>
+  <r>
+    <n v="128"/>
+    <n v="19"/>
+    <x v="56"/>
+    <n v="3"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="91"/>
+  </r>
+  <r>
+    <n v="129"/>
+    <n v="15"/>
+    <x v="1"/>
+    <n v="6"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="70"/>
+  </r>
+  <r>
+    <n v="130"/>
+    <n v="24"/>
+    <x v="54"/>
+    <n v="3"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="92"/>
+  </r>
+  <r>
+    <n v="131"/>
+    <n v="10"/>
+    <x v="59"/>
+    <n v="1"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="93"/>
+  </r>
+  <r>
+    <n v="132"/>
+    <n v="9"/>
+    <x v="46"/>
+    <n v="1"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="133"/>
+    <n v="20"/>
+    <x v="23"/>
+    <n v="2"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="134"/>
+    <n v="5"/>
+    <x v="28"/>
+    <n v="6"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="94"/>
+  </r>
+  <r>
+    <n v="135"/>
+    <n v="1"/>
+    <x v="52"/>
+    <n v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="69"/>
+  </r>
+  <r>
+    <n v="136"/>
+    <n v="1"/>
+    <x v="60"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="82"/>
+  </r>
+  <r>
+    <n v="137"/>
+    <n v="25"/>
+    <x v="11"/>
+    <n v="7"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <n v="138"/>
+    <n v="18"/>
+    <x v="8"/>
+    <n v="1"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="95"/>
+  </r>
+  <r>
+    <n v="139"/>
+    <n v="19"/>
+    <x v="68"/>
+    <n v="3"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="91"/>
+  </r>
+  <r>
+    <n v="140"/>
+    <n v="1"/>
+    <x v="40"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="96"/>
+  </r>
+  <r>
+    <n v="141"/>
+    <n v="18"/>
+    <x v="65"/>
+    <n v="2"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="97"/>
+  </r>
+  <r>
+    <n v="142"/>
+    <n v="11"/>
+    <x v="63"/>
+    <n v="2"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="85"/>
+  </r>
+  <r>
+    <n v="143"/>
+    <n v="24"/>
+    <x v="53"/>
+    <n v="6"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <n v="144"/>
+    <n v="5"/>
+    <x v="43"/>
+    <n v="9"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="98"/>
+  </r>
+  <r>
+    <n v="145"/>
+    <n v="9"/>
+    <x v="15"/>
+    <n v="1"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="146"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="147"/>
+    <n v="12"/>
+    <x v="7"/>
+    <n v="1"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="99"/>
+  </r>
+  <r>
+    <n v="148"/>
+    <n v="24"/>
+    <x v="58"/>
+    <n v="1"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="62"/>
+  </r>
+  <r>
+    <n v="149"/>
+    <n v="7"/>
+    <x v="52"/>
+    <n v="1"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="100"/>
+  </r>
+  <r>
+    <n v="150"/>
+    <n v="24"/>
+    <x v="69"/>
+    <n v="3"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="92"/>
+  </r>
+  <r>
+    <n v="151"/>
+    <n v="23"/>
+    <x v="70"/>
+    <n v="1"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <n v="152"/>
+    <n v="24"/>
+    <x v="27"/>
+    <n v="5"/>
+    <x v="23"/>
+    <x v="4"/>
+    <x v="23"/>
+    <x v="101"/>
+  </r>
+  <r>
+    <n v="153"/>
+    <n v="4"/>
+    <x v="27"/>
+    <n v="4"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="67"/>
+  </r>
+  <r>
+    <n v="154"/>
+    <n v="8"/>
+    <x v="49"/>
+    <n v="1"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="102"/>
+  </r>
+  <r>
+    <n v="155"/>
+    <n v="11"/>
+    <x v="49"/>
+    <n v="4"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="83"/>
+  </r>
+  <r>
+    <n v="156"/>
+    <n v="12"/>
+    <x v="71"/>
+    <n v="2"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="52"/>
+  </r>
+  <r>
+    <n v="157"/>
+    <n v="16"/>
+    <x v="7"/>
+    <n v="1"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="90"/>
+  </r>
+  <r>
+    <n v="158"/>
+    <n v="25"/>
+    <x v="23"/>
+    <n v="2"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="103"/>
+  </r>
+  <r>
+    <n v="159"/>
+    <n v="13"/>
+    <x v="69"/>
+    <n v="2"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <n v="160"/>
+    <n v="5"/>
+    <x v="55"/>
+    <n v="6"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="94"/>
+  </r>
+  <r>
+    <n v="161"/>
+    <n v="15"/>
+    <x v="5"/>
+    <n v="4"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="48"/>
+  </r>
+  <r>
+    <n v="162"/>
+    <n v="11"/>
+    <x v="8"/>
+    <n v="4"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="83"/>
+  </r>
+  <r>
+    <n v="163"/>
+    <n v="14"/>
+    <x v="72"/>
+    <n v="4"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="71"/>
+  </r>
+  <r>
+    <n v="164"/>
+    <n v="15"/>
+    <x v="72"/>
+    <n v="4"/>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="48"/>
+  </r>
+  <r>
+    <n v="165"/>
+    <n v="5"/>
+    <x v="52"/>
+    <n v="7"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="104"/>
+  </r>
+  <r>
+    <n v="166"/>
+    <n v="18"/>
+    <x v="72"/>
+    <n v="2"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="97"/>
+  </r>
+  <r>
+    <n v="167"/>
+    <n v="3"/>
+    <x v="24"/>
+    <n v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="84"/>
+  </r>
+  <r>
+    <n v="168"/>
+    <n v="10"/>
+    <x v="67"/>
+    <n v="3"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="169"/>
+    <n v="25"/>
+    <x v="3"/>
+    <n v="8"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="105"/>
+  </r>
+  <r>
+    <n v="170"/>
+    <n v="18"/>
+    <x v="73"/>
+    <n v="3"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="65"/>
+  </r>
+  <r>
+    <n v="171"/>
+    <n v="16"/>
+    <x v="71"/>
+    <n v="4"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="172"/>
+    <n v="4"/>
+    <x v="50"/>
+    <n v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="106"/>
+  </r>
+  <r>
+    <n v="173"/>
+    <n v="25"/>
+    <x v="38"/>
+    <n v="6"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="56"/>
+  </r>
+  <r>
+    <n v="174"/>
+    <n v="25"/>
+    <x v="74"/>
+    <n v="2"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="103"/>
+  </r>
+  <r>
+    <n v="175"/>
+    <n v="6"/>
+    <x v="66"/>
+    <n v="3"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="107"/>
+  </r>
+  <r>
+    <n v="176"/>
+    <n v="6"/>
+    <x v="6"/>
+    <n v="1"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="45"/>
+  </r>
+  <r>
+    <n v="177"/>
+    <n v="20"/>
+    <x v="46"/>
+    <n v="2"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="178"/>
+    <n v="10"/>
+    <x v="53"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <n v="179"/>
+    <n v="22"/>
+    <x v="11"/>
+    <n v="2"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="108"/>
+  </r>
+  <r>
+    <n v="180"/>
+    <n v="16"/>
+    <x v="48"/>
+    <n v="1"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="90"/>
+  </r>
+  <r>
+    <n v="181"/>
+    <n v="12"/>
+    <x v="67"/>
+    <n v="5"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="109"/>
+  </r>
+  <r>
+    <n v="182"/>
+    <n v="17"/>
+    <x v="8"/>
+    <n v="3"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="110"/>
+  </r>
+  <r>
+    <n v="183"/>
+    <n v="5"/>
+    <x v="46"/>
+    <n v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="73"/>
+  </r>
+  <r>
+    <n v="184"/>
+    <n v="16"/>
+    <x v="75"/>
+    <n v="5"/>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="88"/>
+  </r>
+  <r>
+    <n v="185"/>
+    <n v="5"/>
+    <x v="24"/>
+    <n v="5"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <n v="186"/>
+    <n v="13"/>
+    <x v="43"/>
+    <n v="5"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="77"/>
+  </r>
+  <r>
+    <n v="187"/>
+    <n v="10"/>
+    <x v="33"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <n v="188"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="75"/>
+  </r>
+  <r>
+    <n v="189"/>
+    <n v="12"/>
+    <x v="18"/>
+    <n v="6"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="111"/>
+  </r>
+  <r>
+    <n v="190"/>
+    <n v="23"/>
+    <x v="49"/>
+    <n v="5"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="112"/>
+  </r>
+  <r>
+    <n v="191"/>
+    <n v="19"/>
+    <x v="16"/>
+    <n v="4"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="46"/>
+  </r>
+  <r>
+    <n v="192"/>
+    <n v="8"/>
+    <x v="74"/>
+    <n v="2"/>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <n v="193"/>
+    <n v="25"/>
+    <x v="52"/>
+    <n v="5"/>
+    <x v="24"/>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="113"/>
+  </r>
+  <r>
+    <n v="194"/>
+    <n v="4"/>
+    <x v="34"/>
+    <n v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="114"/>
+  </r>
+  <r>
+    <n v="195"/>
+    <n v="23"/>
+    <x v="69"/>
+    <n v="2"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="115"/>
+  </r>
+  <r>
+    <n v="196"/>
+    <n v="18"/>
+    <x v="42"/>
+    <n v="2"/>
+    <x v="17"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="97"/>
+  </r>
+  <r>
+    <n v="197"/>
+    <n v="1"/>
+    <x v="73"/>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="55"/>
+  </r>
+  <r>
+    <n v="198"/>
+    <n v="23"/>
+    <x v="17"/>
+    <n v="6"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="22"/>
+    <x v="116"/>
+  </r>
+  <r>
+    <n v="199"/>
+    <n v="20"/>
+    <x v="44"/>
+    <n v="1"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="72"/>
+  </r>
+  <r>
+    <n v="200"/>
+    <n v="19"/>
+    <x v="9"/>
+    <n v="5"/>
+    <x v="18"/>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="81"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="55">
   <r>
     <n v="1"/>
@@ -1561,1615 +3575,10 @@
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="200">
-  <r>
-    <x v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="3"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="4"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="4"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="5"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <n v="11"/>
-    <x v="10"/>
-    <x v="5"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <n v="12"/>
-    <x v="11"/>
-    <x v="6"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <n v="13"/>
-    <x v="12"/>
-    <x v="7"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <n v="14"/>
-    <x v="13"/>
-    <x v="1"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="14"/>
-    <n v="15"/>
-    <x v="14"/>
-    <x v="4"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <n v="16"/>
-    <x v="15"/>
-    <x v="6"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <n v="17"/>
-    <x v="16"/>
-    <x v="3"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="17"/>
-    <n v="18"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="18"/>
-    <n v="19"/>
-    <x v="17"/>
-    <x v="5"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <n v="20"/>
-    <x v="18"/>
-    <x v="3"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <n v="21"/>
-    <x v="10"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <n v="22"/>
-    <x v="19"/>
-    <x v="4"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <n v="23"/>
-    <x v="7"/>
-    <x v="5"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <n v="24"/>
-    <x v="14"/>
-    <x v="0"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <n v="25"/>
-    <x v="20"/>
-    <x v="6"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <n v="13"/>
-    <x v="10"/>
-    <x v="3"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="26"/>
-    <n v="2"/>
-    <x v="21"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <n v="24"/>
-    <x v="22"/>
-    <x v="7"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <n v="5"/>
-    <x v="23"/>
-    <x v="9"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="29"/>
-    <n v="22"/>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="30"/>
-    <n v="8"/>
-    <x v="24"/>
-    <x v="3"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <n v="9"/>
-    <x v="25"/>
-    <x v="4"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <n v="17"/>
-    <x v="26"/>
-    <x v="5"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="33"/>
-    <n v="12"/>
-    <x v="1"/>
-    <x v="4"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <n v="11"/>
-    <x v="27"/>
-    <x v="1"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <n v="21"/>
-    <x v="28"/>
-    <x v="5"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="36"/>
-    <n v="5"/>
-    <x v="29"/>
-    <x v="1"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="37"/>
-    <n v="17"/>
-    <x v="30"/>
-    <x v="6"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <n v="21"/>
-    <x v="31"/>
-    <x v="1"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="39"/>
-    <n v="10"/>
-    <x v="32"/>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <n v="15"/>
-    <x v="27"/>
-    <x v="1"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <n v="20"/>
-    <x v="10"/>
-    <x v="6"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="42"/>
-    <n v="23"/>
-    <x v="33"/>
-    <x v="4"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <n v="10"/>
-    <x v="5"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <n v="9"/>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="45"/>
-    <n v="7"/>
-    <x v="11"/>
-    <x v="3"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="46"/>
-    <n v="25"/>
-    <x v="34"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <n v="6"/>
-    <x v="35"/>
-    <x v="3"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="48"/>
-    <n v="23"/>
-    <x v="36"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="49"/>
-    <n v="6"/>
-    <x v="25"/>
-    <x v="5"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="50"/>
-    <n v="19"/>
-    <x v="37"/>
-    <x v="6"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="51"/>
-    <n v="22"/>
-    <x v="38"/>
-    <x v="5"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="52"/>
-    <n v="15"/>
-    <x v="12"/>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="53"/>
-    <n v="3"/>
-    <x v="39"/>
-    <x v="5"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="54"/>
-    <n v="15"/>
-    <x v="40"/>
-    <x v="3"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="55"/>
-    <n v="14"/>
-    <x v="41"/>
-    <x v="4"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="56"/>
-    <n v="12"/>
-    <x v="42"/>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="57"/>
-    <n v="10"/>
-    <x v="22"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="58"/>
-    <n v="1"/>
-    <x v="38"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="59"/>
-    <n v="11"/>
-    <x v="43"/>
-    <x v="4"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="60"/>
-    <n v="1"/>
-    <x v="44"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="61"/>
-    <n v="25"/>
-    <x v="11"/>
-    <x v="7"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="62"/>
-    <n v="9"/>
-    <x v="45"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="63"/>
-    <n v="19"/>
-    <x v="24"/>
-    <x v="5"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <n v="21"/>
-    <x v="29"/>
-    <x v="6"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="65"/>
-    <n v="5"/>
-    <x v="46"/>
-    <x v="6"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="66"/>
-    <n v="2"/>
-    <x v="5"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="67"/>
-    <n v="14"/>
-    <x v="19"/>
-    <x v="7"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="68"/>
-    <n v="24"/>
-    <x v="43"/>
-    <x v="5"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="69"/>
-    <n v="20"/>
-    <x v="19"/>
-    <x v="3"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="70"/>
-    <n v="8"/>
-    <x v="47"/>
-    <x v="3"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="71"/>
-    <n v="2"/>
-    <x v="39"/>
-    <x v="5"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="72"/>
-    <n v="25"/>
-    <x v="48"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="73"/>
-    <n v="25"/>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="74"/>
-    <n v="21"/>
-    <x v="49"/>
-    <x v="3"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="75"/>
-    <n v="19"/>
-    <x v="30"/>
-    <x v="5"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="76"/>
-    <n v="17"/>
-    <x v="50"/>
-    <x v="5"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="77"/>
-    <n v="11"/>
-    <x v="3"/>
-    <x v="5"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="78"/>
-    <n v="18"/>
-    <x v="51"/>
-    <x v="4"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="79"/>
-    <n v="17"/>
-    <x v="52"/>
-    <x v="1"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="80"/>
-    <n v="4"/>
-    <x v="53"/>
-    <x v="6"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="81"/>
-    <n v="2"/>
-    <x v="20"/>
-    <x v="7"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="82"/>
-    <n v="1"/>
-    <x v="29"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="83"/>
-    <n v="15"/>
-    <x v="54"/>
-    <x v="7"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="84"/>
-    <n v="14"/>
-    <x v="32"/>
-    <x v="6"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="85"/>
-    <n v="20"/>
-    <x v="42"/>
-    <x v="5"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="86"/>
-    <n v="5"/>
-    <x v="13"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="87"/>
-    <n v="24"/>
-    <x v="55"/>
-    <x v="8"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="88"/>
-    <n v="22"/>
-    <x v="56"/>
-    <x v="1"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="89"/>
-    <n v="24"/>
-    <x v="46"/>
-    <x v="6"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="90"/>
-    <n v="25"/>
-    <x v="6"/>
-    <x v="7"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="91"/>
-    <n v="22"/>
-    <x v="57"/>
-    <x v="1"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="92"/>
-    <n v="12"/>
-    <x v="58"/>
-    <x v="6"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <n v="17"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="94"/>
-    <n v="13"/>
-    <x v="37"/>
-    <x v="1"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="95"/>
-    <n v="25"/>
-    <x v="8"/>
-    <x v="7"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <n v="9"/>
-    <x v="24"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="97"/>
-    <n v="1"/>
-    <x v="59"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="98"/>
-    <n v="13"/>
-    <x v="34"/>
-    <x v="5"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="99"/>
-    <n v="7"/>
-    <x v="57"/>
-    <x v="3"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="100"/>
-    <n v="9"/>
-    <x v="16"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="101"/>
-    <n v="11"/>
-    <x v="59"/>
-    <x v="4"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="102"/>
-    <n v="4"/>
-    <x v="9"/>
-    <x v="8"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="103"/>
-    <n v="21"/>
-    <x v="29"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="104"/>
-    <n v="19"/>
-    <x v="44"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="105"/>
-    <n v="17"/>
-    <x v="60"/>
-    <x v="6"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="106"/>
-    <n v="8"/>
-    <x v="61"/>
-    <x v="4"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="107"/>
-    <n v="15"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="108"/>
-    <n v="6"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="109"/>
-    <n v="1"/>
-    <x v="62"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="110"/>
-    <n v="11"/>
-    <x v="16"/>
-    <x v="6"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <n v="24"/>
-    <x v="49"/>
-    <x v="7"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="112"/>
-    <n v="3"/>
-    <x v="40"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="113"/>
-    <n v="19"/>
-    <x v="22"/>
-    <x v="5"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="114"/>
-    <n v="24"/>
-    <x v="63"/>
-    <x v="5"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="115"/>
-    <n v="11"/>
-    <x v="64"/>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="116"/>
-    <n v="9"/>
-    <x v="65"/>
-    <x v="4"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="117"/>
-    <n v="14"/>
-    <x v="66"/>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="118"/>
-    <n v="10"/>
-    <x v="33"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="119"/>
-    <n v="2"/>
-    <x v="46"/>
-    <x v="5"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="120"/>
-    <n v="3"/>
-    <x v="42"/>
-    <x v="6"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="121"/>
-    <n v="23"/>
-    <x v="19"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="122"/>
-    <n v="16"/>
-    <x v="28"/>
-    <x v="1"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="123"/>
-    <n v="15"/>
-    <x v="56"/>
-    <x v="4"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="124"/>
-    <n v="23"/>
-    <x v="67"/>
-    <x v="0"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="125"/>
-    <n v="16"/>
-    <x v="28"/>
-    <x v="1"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="126"/>
-    <n v="16"/>
-    <x v="24"/>
-    <x v="5"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="127"/>
-    <n v="19"/>
-    <x v="56"/>
-    <x v="4"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="128"/>
-    <n v="15"/>
-    <x v="1"/>
-    <x v="7"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="129"/>
-    <n v="24"/>
-    <x v="54"/>
-    <x v="4"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="130"/>
-    <n v="10"/>
-    <x v="59"/>
-    <x v="5"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="131"/>
-    <n v="9"/>
-    <x v="46"/>
-    <x v="5"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="132"/>
-    <n v="20"/>
-    <x v="23"/>
-    <x v="3"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="133"/>
-    <n v="5"/>
-    <x v="28"/>
-    <x v="7"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="134"/>
-    <n v="1"/>
-    <x v="52"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="135"/>
-    <n v="1"/>
-    <x v="60"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="136"/>
-    <n v="25"/>
-    <x v="11"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="137"/>
-    <n v="18"/>
-    <x v="8"/>
-    <x v="5"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="138"/>
-    <n v="19"/>
-    <x v="68"/>
-    <x v="4"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="139"/>
-    <n v="1"/>
-    <x v="40"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="140"/>
-    <n v="18"/>
-    <x v="65"/>
-    <x v="3"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="141"/>
-    <n v="11"/>
-    <x v="63"/>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="142"/>
-    <n v="24"/>
-    <x v="53"/>
-    <x v="7"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <n v="5"/>
-    <x v="43"/>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="144"/>
-    <n v="9"/>
-    <x v="15"/>
-    <x v="5"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="145"/>
-    <n v="10"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="146"/>
-    <n v="12"/>
-    <x v="7"/>
-    <x v="5"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="147"/>
-    <n v="24"/>
-    <x v="58"/>
-    <x v="5"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="148"/>
-    <n v="7"/>
-    <x v="52"/>
-    <x v="5"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="149"/>
-    <n v="24"/>
-    <x v="69"/>
-    <x v="4"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="150"/>
-    <n v="23"/>
-    <x v="70"/>
-    <x v="5"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="151"/>
-    <n v="24"/>
-    <x v="27"/>
-    <x v="1"/>
-    <x v="23"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="152"/>
-    <n v="4"/>
-    <x v="27"/>
-    <x v="6"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="153"/>
-    <n v="8"/>
-    <x v="49"/>
-    <x v="5"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="154"/>
-    <n v="11"/>
-    <x v="49"/>
-    <x v="6"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="155"/>
-    <n v="12"/>
-    <x v="71"/>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="156"/>
-    <n v="16"/>
-    <x v="7"/>
-    <x v="5"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="157"/>
-    <n v="25"/>
-    <x v="23"/>
-    <x v="3"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="158"/>
-    <n v="13"/>
-    <x v="69"/>
-    <x v="3"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="159"/>
-    <n v="5"/>
-    <x v="55"/>
-    <x v="7"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <n v="15"/>
-    <x v="5"/>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="161"/>
-    <n v="11"/>
-    <x v="8"/>
-    <x v="6"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="162"/>
-    <n v="14"/>
-    <x v="72"/>
-    <x v="6"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="163"/>
-    <n v="15"/>
-    <x v="72"/>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="164"/>
-    <n v="5"/>
-    <x v="52"/>
-    <x v="8"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="165"/>
-    <n v="18"/>
-    <x v="72"/>
-    <x v="3"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="166"/>
-    <n v="3"/>
-    <x v="24"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="167"/>
-    <n v="10"/>
-    <x v="67"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="168"/>
-    <n v="25"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="169"/>
-    <n v="18"/>
-    <x v="73"/>
-    <x v="4"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="170"/>
-    <n v="16"/>
-    <x v="71"/>
-    <x v="6"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="171"/>
-    <n v="4"/>
-    <x v="50"/>
-    <x v="5"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="172"/>
-    <n v="25"/>
-    <x v="38"/>
-    <x v="7"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <n v="25"/>
-    <x v="74"/>
-    <x v="3"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="174"/>
-    <n v="6"/>
-    <x v="66"/>
-    <x v="4"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="175"/>
-    <n v="6"/>
-    <x v="6"/>
-    <x v="5"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="176"/>
-    <n v="20"/>
-    <x v="46"/>
-    <x v="3"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="177"/>
-    <n v="10"/>
-    <x v="53"/>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="178"/>
-    <n v="22"/>
-    <x v="11"/>
-    <x v="3"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="179"/>
-    <n v="16"/>
-    <x v="48"/>
-    <x v="5"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="180"/>
-    <n v="12"/>
-    <x v="67"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="181"/>
-    <n v="17"/>
-    <x v="8"/>
-    <x v="4"/>
-    <x v="16"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="182"/>
-    <n v="5"/>
-    <x v="46"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="183"/>
-    <n v="16"/>
-    <x v="75"/>
-    <x v="1"/>
-    <x v="15"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="184"/>
-    <n v="5"/>
-    <x v="24"/>
-    <x v="1"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="185"/>
-    <n v="13"/>
-    <x v="43"/>
-    <x v="1"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="186"/>
-    <n v="10"/>
-    <x v="33"/>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="187"/>
-    <n v="22"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="21"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <n v="12"/>
-    <x v="18"/>
-    <x v="7"/>
-    <x v="11"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="189"/>
-    <n v="23"/>
-    <x v="49"/>
-    <x v="1"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <n v="19"/>
-    <x v="16"/>
-    <x v="6"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="191"/>
-    <n v="8"/>
-    <x v="74"/>
-    <x v="3"/>
-    <x v="7"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="192"/>
-    <n v="25"/>
-    <x v="52"/>
-    <x v="1"/>
-    <x v="24"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="193"/>
-    <n v="4"/>
-    <x v="34"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="194"/>
-    <n v="23"/>
-    <x v="69"/>
-    <x v="3"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="195"/>
-    <n v="18"/>
-    <x v="42"/>
-    <x v="3"/>
-    <x v="17"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="196"/>
-    <n v="1"/>
-    <x v="73"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="197"/>
-    <n v="23"/>
-    <x v="17"/>
-    <x v="7"/>
-    <x v="22"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="198"/>
-    <n v="20"/>
-    <x v="44"/>
-    <x v="5"/>
-    <x v="19"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="199"/>
-    <n v="19"/>
-    <x v="9"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="3"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8704B360-FE44-494C-94B4-1A23F8608829}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8704B360-FE44-494C-94B4-1A23F8608829}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
+  <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -3566,6 +3975,8 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="15">
         <item x="0"/>
@@ -3636,10 +4047,407 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{736C1CFA-B73E-A24B-B772-CD5077B79836}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H3:K10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="118">
+        <item x="63"/>
+        <item x="31"/>
+        <item x="49"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="72"/>
+        <item x="106"/>
+        <item x="110"/>
+        <item x="84"/>
+        <item x="1"/>
+        <item x="73"/>
+        <item x="36"/>
+        <item x="68"/>
+        <item x="19"/>
+        <item x="96"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="114"/>
+        <item x="45"/>
+        <item x="34"/>
+        <item x="87"/>
+        <item x="35"/>
+        <item x="86"/>
+        <item x="78"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="104"/>
+        <item x="10"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="90"/>
+        <item x="98"/>
+        <item x="67"/>
+        <item x="5"/>
+        <item x="64"/>
+        <item x="82"/>
+        <item x="27"/>
+        <item x="47"/>
+        <item x="2"/>
+        <item x="99"/>
+        <item x="97"/>
+        <item x="107"/>
+        <item x="53"/>
+        <item x="85"/>
+        <item x="62"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="50"/>
+        <item x="0"/>
+        <item x="22"/>
+        <item x="51"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="65"/>
+        <item x="58"/>
+        <item x="55"/>
+        <item x="108"/>
+        <item x="54"/>
+        <item x="71"/>
+        <item x="52"/>
+        <item x="93"/>
+        <item x="37"/>
+        <item x="91"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="46"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="115"/>
+        <item x="61"/>
+        <item x="32"/>
+        <item x="100"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="81"/>
+        <item x="39"/>
+        <item x="102"/>
+        <item x="88"/>
+        <item x="11"/>
+        <item x="38"/>
+        <item x="92"/>
+        <item x="70"/>
+        <item x="41"/>
+        <item x="57"/>
+        <item x="75"/>
+        <item x="109"/>
+        <item x="24"/>
+        <item x="76"/>
+        <item x="111"/>
+        <item x="9"/>
+        <item x="42"/>
+        <item x="113"/>
+        <item x="28"/>
+        <item x="101"/>
+        <item x="77"/>
+        <item x="30"/>
+        <item x="112"/>
+        <item x="29"/>
+        <item x="56"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="116"/>
+        <item x="43"/>
+        <item x="6"/>
+        <item x="74"/>
+        <item x="44"/>
+        <item x="105"/>
+        <item x="23"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of revenue" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E04A2F7E-3F55-FE46-B0DB-67A3C27063F4}" name="PivotTable2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="118">
+        <item x="63"/>
+        <item x="31"/>
+        <item x="49"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="72"/>
+        <item x="106"/>
+        <item x="110"/>
+        <item x="84"/>
+        <item x="1"/>
+        <item x="73"/>
+        <item x="36"/>
+        <item x="68"/>
+        <item x="19"/>
+        <item x="96"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="114"/>
+        <item x="45"/>
+        <item x="34"/>
+        <item x="87"/>
+        <item x="35"/>
+        <item x="86"/>
+        <item x="78"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="104"/>
+        <item x="10"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="90"/>
+        <item x="98"/>
+        <item x="67"/>
+        <item x="5"/>
+        <item x="64"/>
+        <item x="82"/>
+        <item x="27"/>
+        <item x="47"/>
+        <item x="2"/>
+        <item x="99"/>
+        <item x="97"/>
+        <item x="107"/>
+        <item x="53"/>
+        <item x="85"/>
+        <item x="62"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="50"/>
+        <item x="0"/>
+        <item x="22"/>
+        <item x="51"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="65"/>
+        <item x="58"/>
+        <item x="55"/>
+        <item x="108"/>
+        <item x="54"/>
+        <item x="71"/>
+        <item x="52"/>
+        <item x="93"/>
+        <item x="37"/>
+        <item x="91"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="46"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="115"/>
+        <item x="61"/>
+        <item x="32"/>
+        <item x="100"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="81"/>
+        <item x="39"/>
+        <item x="102"/>
+        <item x="88"/>
+        <item x="11"/>
+        <item x="38"/>
+        <item x="92"/>
+        <item x="70"/>
+        <item x="41"/>
+        <item x="57"/>
+        <item x="75"/>
+        <item x="109"/>
+        <item x="24"/>
+        <item x="76"/>
+        <item x="111"/>
+        <item x="9"/>
+        <item x="42"/>
+        <item x="113"/>
+        <item x="28"/>
+        <item x="101"/>
+        <item x="77"/>
+        <item x="30"/>
+        <item x="112"/>
+        <item x="29"/>
+        <item x="56"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="116"/>
+        <item x="43"/>
+        <item x="6"/>
+        <item x="74"/>
+        <item x="44"/>
+        <item x="105"/>
+        <item x="23"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of revenue" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{775F00E6-634C-A044-92B7-1B1761838D30}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{775F00E6-634C-A044-92B7-1B1761838D30}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D36" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
-  <pivotFields count="7">
+  <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" numFmtId="14" showAll="0">
@@ -4056,6 +4864,8 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="15">
         <item h="1" sd="0" x="0"/>
@@ -4176,7 +4986,7 @@
     </i>
   </rowItems>
   <colFields count="2">
-    <field x="6"/>
+    <field x="8"/>
     <field x="2"/>
   </colFields>
   <colItems count="3">
@@ -4206,7 +5016,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A31DB849-6901-8A4A-B833-4AC084DEC07C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A31DB849-6901-8A4A-B833-4AC084DEC07C}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -4307,214 +5117,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DFC7A411-36E7-A443-B507-E7B7735230CB}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DFC7A411-36E7-A443-B507-E7B7735230CB}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I3:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0">
-      <items count="201">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+  <pivotFields count="9">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
@@ -4529,6 +5135,8 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
       <items count="14">
         <item h="1" x="0"/>
@@ -4572,7 +5180,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="6"/>
+    <field x="8"/>
   </colFields>
   <colItems count="3">
     <i>
@@ -4601,9 +5209,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8D3C8C2-6CE8-2546-B6A4-5FDEB58E7400}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8D3C8C2-6CE8-2546-B6A4-5FDEB58E7400}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
+  <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -4979,21 +5587,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="11">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -5016,7 +5612,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="6"/>
+    <field x="8"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="5">
@@ -5064,9 +5660,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFAA042B-8795-AC4A-A0B5-B6421579EDED}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFAA042B-8795-AC4A-A0B5-B6421579EDED}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="X3:AA30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="7">
+  <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
@@ -5101,6 +5697,8 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="14">
@@ -5214,7 +5812,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="6"/>
+    <field x="8"/>
   </colFields>
   <colItems count="3">
     <i>
@@ -5243,214 +5841,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C7B761C-AD45-BF41-944D-86B53595C150}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C7B761C-AD45-BF41-944D-86B53595C150}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Q3:T30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0">
-      <items count="201">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+  <pivotFields count="9">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
@@ -5484,6 +5878,8 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
       <items count="14">
@@ -5588,7 +5984,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="6"/>
+    <field x="8"/>
   </colFields>
   <colItems count="3">
     <i>
@@ -5603,6 +5999,411 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Count of sale_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BF6217C-1F35-8243-AF90-509C8F69F245}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="W3:Z10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item h="1" x="10"/>
+        <item x="5"/>
+        <item h="1" x="16"/>
+        <item x="7"/>
+        <item h="1" x="23"/>
+        <item x="6"/>
+        <item h="1" x="19"/>
+        <item h="1" x="2"/>
+        <item x="24"/>
+        <item h="1" x="8"/>
+        <item h="1" x="18"/>
+        <item h="1" x="4"/>
+        <item h="1" x="21"/>
+        <item h="1" x="15"/>
+        <item h="1" x="12"/>
+        <item h="1" x="17"/>
+        <item h="1" x="13"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="22"/>
+        <item x="20"/>
+        <item h="1" x="14"/>
+        <item h="1" x="11"/>
+        <item h="1" x="0"/>
+        <item h="1" x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="26">
+        <item x="1"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="21"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of unit_price" fld="6" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9159BD7F-EE74-D44D-8A81-DFD1CDB4F165}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="P3:S17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item x="10"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="19"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="21"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="118">
+        <item x="63"/>
+        <item x="31"/>
+        <item x="49"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="72"/>
+        <item x="106"/>
+        <item x="110"/>
+        <item x="84"/>
+        <item x="1"/>
+        <item x="73"/>
+        <item x="36"/>
+        <item x="68"/>
+        <item x="19"/>
+        <item x="96"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="114"/>
+        <item x="45"/>
+        <item x="34"/>
+        <item x="87"/>
+        <item x="35"/>
+        <item x="86"/>
+        <item x="78"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="104"/>
+        <item x="10"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="90"/>
+        <item x="98"/>
+        <item x="67"/>
+        <item x="5"/>
+        <item x="64"/>
+        <item x="82"/>
+        <item x="27"/>
+        <item x="47"/>
+        <item x="2"/>
+        <item x="99"/>
+        <item x="97"/>
+        <item x="107"/>
+        <item x="53"/>
+        <item x="85"/>
+        <item x="62"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="50"/>
+        <item x="0"/>
+        <item x="22"/>
+        <item x="51"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="65"/>
+        <item x="58"/>
+        <item x="55"/>
+        <item x="108"/>
+        <item x="54"/>
+        <item x="71"/>
+        <item x="52"/>
+        <item x="93"/>
+        <item x="37"/>
+        <item x="91"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="46"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="115"/>
+        <item x="61"/>
+        <item x="32"/>
+        <item x="100"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="81"/>
+        <item x="39"/>
+        <item x="102"/>
+        <item x="88"/>
+        <item x="11"/>
+        <item x="38"/>
+        <item x="92"/>
+        <item x="70"/>
+        <item x="41"/>
+        <item x="57"/>
+        <item x="75"/>
+        <item x="109"/>
+        <item x="24"/>
+        <item x="76"/>
+        <item x="111"/>
+        <item x="9"/>
+        <item x="42"/>
+        <item x="113"/>
+        <item x="28"/>
+        <item x="101"/>
+        <item x="77"/>
+        <item x="30"/>
+        <item x="112"/>
+        <item x="29"/>
+        <item x="56"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="116"/>
+        <item x="43"/>
+        <item x="6"/>
+        <item x="74"/>
+        <item x="44"/>
+        <item x="105"/>
+        <item x="23"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="5"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of revenue" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -14480,25 +15281,25 @@
   <dimension ref="A1:AD30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.5" customWidth="1"/>
+    <col min="19" max="19" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83203125" customWidth="1"/>
+    <col min="26" max="26" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="4.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -14543,13 +15344,13 @@
       <c r="C3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -14597,10 +15398,10 @@
       <c r="L4" t="s">
         <v>39</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -15474,9 +16275,637 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5CEE3E-5384-C044-9B81-0086432F95DA}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.1640625" customWidth="1"/>
+    <col min="19" max="19" width="15.1640625" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.1640625" customWidth="1"/>
+    <col min="26" max="27" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="H1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="P1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="P3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4">
+        <v>57237.80999999999</v>
+      </c>
+      <c r="E4">
+        <f>57237.81 / 61</f>
+        <v>938.32475409836059</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4">
+        <v>42551.470000000008</v>
+      </c>
+      <c r="C5">
+        <f>42551.47-57237.81</f>
+        <v>-14686.339999999997</v>
+      </c>
+      <c r="D5">
+        <f>C5/GETPIVOTDATA("revenue",$A$3,"Months",7)*100</f>
+        <v>-25.658458980174114</v>
+      </c>
+      <c r="E5">
+        <f>42551.47 / 36</f>
+        <v>1181.9852777777778</v>
+      </c>
+      <c r="F5">
+        <f>(1181.985278 - 938.3247541) / 938.3247541 *100</f>
+        <v>25.967611195945551</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="4">
+        <v>3257.14</v>
+      </c>
+      <c r="J5" s="4">
+        <v>701.98</v>
+      </c>
+      <c r="K5" s="4">
+        <v>3959.12</v>
+      </c>
+      <c r="L5">
+        <f>GETPIVOTDATA("revenue",$H$3,"category","Accessories","Months",8)-GETPIVOTDATA("revenue",$H$3,"category","Accessories","Months",7)</f>
+        <v>-2555.16</v>
+      </c>
+      <c r="M5" s="13">
+        <f>L5/GETPIVOTDATA("revenue",$H$3,"category","Accessories","Months",7) *100</f>
+        <v>-78.44796355084523</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>19694.5</v>
+      </c>
+      <c r="R5" s="4">
+        <v>12907.990000000002</v>
+      </c>
+      <c r="S5" s="4">
+        <v>32602.489999999998</v>
+      </c>
+      <c r="T5" s="14">
+        <f>GETPIVOTDATA("revenue",$P$3,"category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"category","Computer","Months",7)</f>
+        <v>-6786.5099999999984</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="X5" s="4">
+        <v>146.37</v>
+      </c>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4">
+        <v>146.37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4">
+        <v>99789.28</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4">
+        <v>8096.37</v>
+      </c>
+      <c r="J6" s="4">
+        <v>6943.71</v>
+      </c>
+      <c r="K6" s="4">
+        <v>15040.08</v>
+      </c>
+      <c r="L6">
+        <f>GETPIVOTDATA("revenue",$H$3,"category","Audio","Months",8)-GETPIVOTDATA("revenue",$H$3,"category","Audio","Months",7)</f>
+        <v>-1152.6599999999999</v>
+      </c>
+      <c r="M6" s="13">
+        <f>L6/GETPIVOTDATA("revenue",$H$3,"category","Audio","Months",7)*100</f>
+        <v>-14.236750543762202</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1024.5900000000001</v>
+      </c>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4">
+        <v>1024.5900000000001</v>
+      </c>
+      <c r="T6">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Business Laptop","category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Business Laptop","category","Computer","Months",7)</f>
+        <v>-1024.5900000000001</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X6" s="4">
+        <v>1387.44</v>
+      </c>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4">
+        <v>1387.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="4">
+        <v>19694.500000000004</v>
+      </c>
+      <c r="J7" s="4">
+        <v>12907.989999999998</v>
+      </c>
+      <c r="K7" s="4">
+        <v>32602.49</v>
+      </c>
+      <c r="L7">
+        <f>GETPIVOTDATA("revenue",$H$3,"category","Computer","Months",8)-GETPIVOTDATA("revenue",$H$3,"category","Computer","Months",7)</f>
+        <v>-6786.5100000000057</v>
+      </c>
+      <c r="M7" s="13">
+        <f>L7/GETPIVOTDATA("revenue",$H$3,"category","Computer","Months",7)*100</f>
+        <v>-34.45890984792711</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>6937.2</v>
+      </c>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4">
+        <v>6937.2</v>
+      </c>
+      <c r="T7">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Desktop Computer","category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Desktop Computer","category","Computer","Months",7)</f>
+        <v>-6937.2</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X7" s="4">
+        <v>1107.2</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>1107.2</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>1107.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="4">
+        <v>20800.13</v>
+      </c>
+      <c r="J8" s="4">
+        <v>14303.65</v>
+      </c>
+      <c r="K8" s="4">
+        <v>35103.78</v>
+      </c>
+      <c r="L8">
+        <f>GETPIVOTDATA("revenue",$H$3,"category","Networking","Months",8)-GETPIVOTDATA("revenue",$H$3,"category","Networking","Months",7)</f>
+        <v>-6496.4800000000014</v>
+      </c>
+      <c r="M8" s="13">
+        <f>L8/GETPIVOTDATA("revenue",$H$3,"category","Networking","Months",7)*100</f>
+        <v>-31.23288171756619</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>3321.6000000000004</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2214.4</v>
+      </c>
+      <c r="S8" s="4">
+        <v>5536</v>
+      </c>
+      <c r="T8">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Gaming Laptop","category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Gaming Laptop","category","Computer","Months",7)</f>
+        <v>-1107.2000000000003</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X8" s="4">
+        <v>472.01000000000005</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>472.01</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>472.01000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="4">
+        <v>5389.67</v>
+      </c>
+      <c r="J9" s="4">
+        <v>7694.1399999999994</v>
+      </c>
+      <c r="K9" s="4">
+        <v>13083.81</v>
+      </c>
+      <c r="L9">
+        <f>GETPIVOTDATA("revenue",$H$3,"category","Office","Months",8)-GETPIVOTDATA("revenue",$H$3,"category","Office","Months",7)</f>
+        <v>2304.4699999999993</v>
+      </c>
+      <c r="M9" s="13">
+        <f>L9/GETPIVOTDATA("revenue",$H$3,"category","Office","Months",7)*100</f>
+        <v>42.757163240049934</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>3379.44</v>
+      </c>
+      <c r="R9" s="4">
+        <v>4224.3</v>
+      </c>
+      <c r="S9" s="4">
+        <v>7603.74</v>
+      </c>
+      <c r="T9">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Mini PC","category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Mini PC","category","Computer","Months",7)</f>
+        <v>844.86000000000013</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="X9" s="4">
+        <v>147.08000000000001</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>147.08000000000001</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>147.08000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="4">
+        <v>57237.81</v>
+      </c>
+      <c r="J10" s="4">
+        <v>42551.47</v>
+      </c>
+      <c r="K10" s="4">
+        <v>99789.28</v>
+      </c>
+      <c r="L10" s="12">
+        <f>GETPIVOTDATA("revenue",$H$3,"Months",8)-GETPIVOTDATA("revenue",$H$3,"Months",7)</f>
+        <v>-14686.339999999997</v>
+      </c>
+      <c r="M10" s="12">
+        <f>L10/GETPIVOTDATA("revenue",$H$3,"Months",7)*100</f>
+        <v>-25.658458980174114</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>5031.67</v>
+      </c>
+      <c r="R10" s="4">
+        <v>6469.29</v>
+      </c>
+      <c r="S10" s="4">
+        <v>11500.96</v>
+      </c>
+      <c r="T10">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Workstation","category","Computer","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Workstation","category","Computer","Months",7)</f>
+        <v>1437.62</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X10" s="4">
+        <v>508.69785714285723</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>575.42999999999995</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>520.47411764705885</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>20800.129999999997</v>
+      </c>
+      <c r="R11" s="4">
+        <v>14303.65</v>
+      </c>
+      <c r="S11" s="4">
+        <v>35103.78</v>
+      </c>
+      <c r="T11" s="14">
+        <f>GETPIVOTDATA("revenue",$P$3,"category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"category","Networking","Months",7)</f>
+        <v>-6496.4799999999977</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>2434.6999999999998</v>
+      </c>
+      <c r="R12" s="4">
+        <v>2921.64</v>
+      </c>
+      <c r="S12" s="4">
+        <v>5356.34</v>
+      </c>
+      <c r="T12">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Ethernet Adapter","category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Ethernet Adapter","category","Networking","Months",7)</f>
+        <v>486.94000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>11800.25</v>
+      </c>
+      <c r="R13" s="4">
+        <v>3304.0699999999997</v>
+      </c>
+      <c r="S13" s="4">
+        <v>15104.32</v>
+      </c>
+      <c r="T13">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Mesh Wi-Fi System","category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Mesh Wi-Fi System","category","Networking","Months",7)</f>
+        <v>-8496.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>3761.1200000000003</v>
+      </c>
+      <c r="R14" s="4">
+        <v>2735.36</v>
+      </c>
+      <c r="S14" s="4">
+        <v>6496.4800000000005</v>
+      </c>
+      <c r="T14">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Network Switch","category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Network Switch","category","Networking","Months",7)</f>
+        <v>-1025.7600000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>1039.0999999999999</v>
+      </c>
+      <c r="R15" s="4">
+        <v>5195.4999999999991</v>
+      </c>
+      <c r="S15" s="4">
+        <v>6234.5999999999985</v>
+      </c>
+      <c r="T15">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Wi-Fi Extender","category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Wi-Fi Extender","category","Networking","Months",7)</f>
+        <v>4156.3999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="P16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>1764.9600000000003</v>
+      </c>
+      <c r="R16" s="4">
+        <v>147.08000000000001</v>
+      </c>
+      <c r="S16" s="4">
+        <v>1912.0400000000002</v>
+      </c>
+      <c r="T16">
+        <f>GETPIVOTDATA("revenue",$P$3,"product_name","Wi-Fi Router","category","Networking","Months",8)-GETPIVOTDATA("revenue",$P$3,"product_name","Wi-Fi Router","category","Networking","Months",7)</f>
+        <v>-1617.8800000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>40494.629999999997</v>
+      </c>
+      <c r="R17" s="4">
+        <v>27211.640000000003</v>
+      </c>
+      <c r="S17" s="4">
+        <v>67706.27</v>
+      </c>
+      <c r="T17" s="12">
+        <f>GETPIVOTDATA("revenue",$P$3,"Months",8)-GETPIVOTDATA("revenue",$P$3,"Months",7)</f>
+        <v>-13282.989999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="16"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="17"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f>57237.81/204</f>
+        <v>280.57749999999999</v>
+      </c>
+      <c r="B32">
+        <f>42551.47/125</f>
+        <v>340.41176000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>